--- a/week-09/NorthwindTablesAndColumns.xlsx
+++ b/week-09/NorthwindTablesAndColumns.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yearuptemp-my.sharepoint.com/personal/hmerawi_my_yearupunited_org/Documents/Desktop/Documents/DataAnalytics/week-09/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="337" documentId="8_{FA878EF4-4B80-439A-88BC-05CECC90D1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B65ED56A-C96F-4078-9582-87882B8EF4B4}"/>
+  <xr:revisionPtr revIDLastSave="634" documentId="8_{FA878EF4-4B80-439A-88BC-05CECC90D1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D97C2BD-06B2-42EA-ADBD-489CF88A4703}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{901F5D27-877F-4C94-89AE-9A9B6ECE5CB6}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="181">
   <si>
     <t>table_name</t>
   </si>
@@ -322,21 +322,9 @@
     <t>No</t>
   </si>
   <si>
-    <t>Category ID</t>
-  </si>
-  <si>
-    <t>Customer ID</t>
-  </si>
-  <si>
-    <t>Employee ID</t>
-  </si>
-  <si>
     <t xml:space="preserve">Category </t>
   </si>
   <si>
-    <t>Customer Name</t>
-  </si>
-  <si>
     <t>Contact Name</t>
   </si>
   <si>
@@ -355,30 +343,12 @@
     <t>Hire Date</t>
   </si>
   <si>
-    <t>Postal Code</t>
-  </si>
-  <si>
     <t>Job title</t>
   </si>
   <si>
-    <t>Manager ID</t>
-  </si>
-  <si>
     <t>NO</t>
   </si>
   <si>
-    <t>Territory ID</t>
-  </si>
-  <si>
-    <t>Order ID</t>
-  </si>
-  <si>
-    <t>Product ID</t>
-  </si>
-  <si>
-    <t>Unit Price</t>
-  </si>
-  <si>
     <t>Order Date</t>
   </si>
   <si>
@@ -391,36 +361,15 @@
     <t>Ship Name</t>
   </si>
   <si>
-    <t>Ship City</t>
-  </si>
-  <si>
-    <t>Ship Region</t>
-  </si>
-  <si>
-    <t>Ship Country</t>
-  </si>
-  <si>
     <t xml:space="preserve">Quantity </t>
   </si>
   <si>
-    <t>Shipped ID</t>
-  </si>
-  <si>
-    <t>Ship Postal Code</t>
-  </si>
-  <si>
-    <t>Shipper ID</t>
-  </si>
-  <si>
     <t>Shipper Name</t>
   </si>
   <si>
     <t xml:space="preserve">Product </t>
   </si>
   <si>
-    <t>Supplier ID</t>
-  </si>
-  <si>
     <t>Quantity Per Unit</t>
   </si>
   <si>
@@ -436,19 +385,199 @@
     <t xml:space="preserve">Is Discontinued </t>
   </si>
   <si>
-    <t xml:space="preserve">Region ID </t>
-  </si>
-  <si>
     <t xml:space="preserve">Region </t>
   </si>
   <si>
     <t>yes</t>
   </si>
   <si>
-    <t>Supplier Name</t>
-  </si>
-  <si>
     <t xml:space="preserve">Territory </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer </t>
+  </si>
+  <si>
+    <t>Customer City</t>
+  </si>
+  <si>
+    <t>Customer Region</t>
+  </si>
+  <si>
+    <t>Customer PostalCode</t>
+  </si>
+  <si>
+    <t>Customer Country</t>
+  </si>
+  <si>
+    <t>Employee City</t>
+  </si>
+  <si>
+    <t>Employee Region</t>
+  </si>
+  <si>
+    <t>Employee Postal Code</t>
+  </si>
+  <si>
+    <t>Employee Country</t>
+  </si>
+  <si>
+    <t>ManagerID</t>
+  </si>
+  <si>
+    <t>Unit Price Amount</t>
+  </si>
+  <si>
+    <t>Discount Amount</t>
+  </si>
+  <si>
+    <t>Freight Amount</t>
+  </si>
+  <si>
+    <t>Order Ship City</t>
+  </si>
+  <si>
+    <t>Order Ship Region</t>
+  </si>
+  <si>
+    <t>Order Ship Postal Code</t>
+  </si>
+  <si>
+    <t>Order Ship Country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplier </t>
+  </si>
+  <si>
+    <t>Supplier City</t>
+  </si>
+  <si>
+    <t>Supplier Region</t>
+  </si>
+  <si>
+    <t>Supplier Postal Code</t>
+  </si>
+  <si>
+    <t>Supplier Country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RegionID </t>
+  </si>
+  <si>
+    <t>ShippedID</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>key used for r/nships only</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>primary descriptor useed to group item on charts</t>
+  </si>
+  <si>
+    <t>re/ship key</t>
+  </si>
+  <si>
+    <t>Primary descriptor for customer slice filters.</t>
+  </si>
+  <si>
+    <t>Used for geographic map visualizations</t>
+  </si>
+  <si>
+    <t>Short Date (MM/DD/YY)</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>used as timeline filters</t>
+  </si>
+  <si>
+    <t>Track employee location</t>
+  </si>
+  <si>
+    <t>Creates organizational hierarchy relationship</t>
+  </si>
+  <si>
+    <t>Bridge table keys  do not display in reports.</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>Avarage,Max,Min</t>
+  </si>
+  <si>
+    <t>Used to track historical item price at time of purchase</t>
+  </si>
+  <si>
+    <t>Whole Number</t>
+  </si>
+  <si>
+    <t>sum</t>
+  </si>
+  <si>
+    <t>Used to calculate total volume of products sold.</t>
+  </si>
+  <si>
+    <t>% or Currency</t>
+  </si>
+  <si>
+    <t>Avarage,Sum</t>
+  </si>
+  <si>
+    <t>Need to verify if database stores this as a flat rate reduction or percentage rate</t>
+  </si>
+  <si>
+    <t>Short Date</t>
+  </si>
+  <si>
+    <t>Core sales timeline analysis</t>
+  </si>
+  <si>
+    <t>Average,Sum</t>
+  </si>
+  <si>
+    <t>used to analyze total Shipping cost paid</t>
+  </si>
+  <si>
+    <t>primary item selector for chart</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>current list price of product</t>
+  </si>
+  <si>
+    <t>Sum, Min</t>
+  </si>
+  <si>
+    <t>Used for inventory levels and low-stock triggers</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Safety threshold for reordering stock.</t>
+  </si>
+  <si>
+    <t>Used as a key catalog status filter</t>
+  </si>
+  <si>
+    <t>True/False</t>
+  </si>
+  <si>
+    <t>Top level operational regional reporting filter</t>
+  </si>
+  <si>
+    <t>Used to analyze shipping performance by carrier.</t>
+  </si>
+  <si>
+    <t>Used to analyze supplier sourcing locations</t>
   </si>
 </sst>
 </file>
@@ -536,6 +665,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -835,7 +968,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6B56A5E-AA28-4DB9-BAE3-51DE131C631E}">
-  <dimension ref="A1:N85"/>
+  <dimension ref="A1:P85"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.88671875" customWidth="1"/>
@@ -848,8 +981,9 @@
     <col min="9" max="9" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.88671875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="26" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5546875" customWidth="1"/>
-    <col min="13" max="13" width="11.5546875" customWidth="1"/>
+    <col min="12" max="12" width="21.77734375" customWidth="1"/>
+    <col min="13" max="13" width="14.77734375" customWidth="1"/>
+    <col min="14" max="14" width="40.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -922,7 +1056,22 @@
         <v>92</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>95</v>
+        <v>6</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -951,7 +1100,22 @@
         <v>92</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -1020,7 +1184,22 @@
         <v>92</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>96</v>
+        <v>14</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1049,7 +1228,22 @@
         <v>92</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>99</v>
+        <v>119</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N7" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1078,7 +1272,19 @@
         <v>92</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1107,7 +1313,19 @@
         <v>92</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1156,7 +1374,22 @@
         <v>92</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>21</v>
+        <v>120</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N11" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1185,7 +1418,22 @@
         <v>92</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>22</v>
+        <v>121</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N12" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1214,7 +1462,22 @@
         <v>92</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>23</v>
+        <v>122</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N13" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1243,7 +1506,22 @@
         <v>92</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>24</v>
+        <v>123</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N14" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1286,7 +1564,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>27</v>
       </c>
@@ -1312,10 +1590,22 @@
         <v>92</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
@@ -1341,10 +1631,22 @@
         <v>92</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -1370,10 +1672,22 @@
         <v>92</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>27</v>
       </c>
@@ -1399,10 +1713,22 @@
         <v>92</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
@@ -1422,7 +1748,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>27</v>
       </c>
@@ -1448,10 +1774,25 @@
         <v>92</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>27</v>
       </c>
@@ -1477,10 +1818,25 @@
         <v>92</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -1500,7 +1856,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>27</v>
       </c>
@@ -1520,16 +1876,31 @@
         <v>94</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H25" t="s">
         <v>92</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -1555,10 +1926,25 @@
         <v>92</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>27</v>
       </c>
@@ -1584,10 +1970,25 @@
         <v>92</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
@@ -1613,10 +2014,25 @@
         <v>92</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
@@ -1636,7 +2052,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>27</v>
       </c>
@@ -1656,7 +2072,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>27</v>
       </c>
@@ -1676,7 +2092,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1696,7 +2112,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>27</v>
       </c>
@@ -1722,10 +2138,25 @@
         <v>92</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="N33" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>27</v>
       </c>
@@ -1745,7 +2176,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>42</v>
       </c>
@@ -1771,10 +2202,25 @@
         <v>92</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N35" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>42</v>
       </c>
@@ -1800,10 +2246,25 @@
         <v>92</v>
       </c>
       <c r="I36" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N36" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>44</v>
       </c>
@@ -1829,10 +2290,22 @@
         <v>92</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>44</v>
       </c>
@@ -1858,10 +2331,22 @@
         <v>92</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>44</v>
       </c>
@@ -1887,10 +2372,25 @@
         <v>92</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="N39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>44</v>
       </c>
@@ -1916,10 +2416,25 @@
         <v>92</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="N40" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>44</v>
       </c>
@@ -1945,10 +2460,25 @@
         <v>92</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="N41" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>53</v>
       </c>
@@ -1974,10 +2504,22 @@
         <v>92</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>53</v>
       </c>
@@ -2003,10 +2545,23 @@
         <v>92</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="P43" s="2"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>53</v>
       </c>
@@ -2032,10 +2587,22 @@
         <v>92</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>53</v>
       </c>
@@ -2061,10 +2628,25 @@
         <v>92</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>53</v>
       </c>
@@ -2090,10 +2672,25 @@
         <v>92</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>53</v>
       </c>
@@ -2119,10 +2716,25 @@
         <v>92</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>53</v>
       </c>
@@ -2148,10 +2760,22 @@
         <v>92</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+        <v>142</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>53</v>
       </c>
@@ -2177,10 +2801,25 @@
         <v>92</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>53</v>
       </c>
@@ -2206,10 +2845,22 @@
         <v>92</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>53</v>
       </c>
@@ -2229,7 +2880,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>53</v>
       </c>
@@ -2255,10 +2906,22 @@
         <v>92</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>53</v>
       </c>
@@ -2284,10 +2947,22 @@
         <v>92</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>53</v>
       </c>
@@ -2313,10 +2988,22 @@
         <v>92</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>53</v>
       </c>
@@ -2342,10 +3029,22 @@
         <v>92</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>65</v>
       </c>
@@ -2371,10 +3070,22 @@
         <v>92</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>65</v>
       </c>
@@ -2400,10 +3111,25 @@
         <v>92</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>65</v>
       </c>
@@ -2429,10 +3155,22 @@
         <v>92</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>65</v>
       </c>
@@ -2458,10 +3196,22 @@
         <v>92</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>65</v>
       </c>
@@ -2487,10 +3237,22 @@
         <v>92</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>65</v>
       </c>
@@ -2516,10 +3278,25 @@
         <v>92</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>65</v>
       </c>
@@ -2545,10 +3322,25 @@
         <v>92</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="N62" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>65</v>
       </c>
@@ -2574,10 +3366,22 @@
         <v>92</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>65</v>
       </c>
@@ -2603,10 +3407,25 @@
         <v>92</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N64" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>65</v>
       </c>
@@ -2632,10 +3451,25 @@
         <v>92</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N65" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>22</v>
       </c>
@@ -2661,10 +3495,22 @@
         <v>92</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>22</v>
       </c>
@@ -2690,10 +3536,25 @@
         <v>92</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N67" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>76</v>
       </c>
@@ -2719,10 +3580,22 @@
         <v>92</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>76</v>
       </c>
@@ -2748,10 +3621,25 @@
         <v>92</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N69" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>76</v>
       </c>
@@ -2772,7 +3660,7 @@
       </c>
       <c r="I70" s="4"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>78</v>
       </c>
@@ -2789,7 +3677,7 @@
         <v>4</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>94</v>
@@ -2798,10 +3686,22 @@
         <v>92</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M71" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>78</v>
       </c>
@@ -2829,8 +3729,20 @@
       <c r="I72" s="4" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J72" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>78</v>
       </c>
@@ -2856,10 +3768,22 @@
         <v>92</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M73" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>78</v>
       </c>
@@ -2885,10 +3809,22 @@
         <v>92</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>78</v>
       </c>
@@ -2909,7 +3845,7 @@
       </c>
       <c r="I75" s="4"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>78</v>
       </c>
@@ -2935,10 +3871,25 @@
         <v>92</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N76" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>78</v>
       </c>
@@ -2964,10 +3915,25 @@
         <v>92</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N77" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>78</v>
       </c>
@@ -2993,10 +3959,25 @@
         <v>92</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M78" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N78" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>78</v>
       </c>
@@ -3022,10 +4003,25 @@
         <v>92</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M79" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N79" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>78</v>
       </c>
@@ -3046,7 +4042,7 @@
       </c>
       <c r="I80" s="4"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>78</v>
       </c>
@@ -3067,7 +4063,7 @@
       </c>
       <c r="I81" s="4"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>78</v>
       </c>
@@ -3088,7 +4084,7 @@
       </c>
       <c r="I82" s="4"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>80</v>
       </c>
@@ -3114,10 +4110,22 @@
         <v>92</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>80</v>
       </c>
@@ -3143,10 +4151,22 @@
         <v>92</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>80</v>
       </c>
@@ -3172,7 +4192,19 @@
         <v>92</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>133</v>
+        <v>141</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/week-09/NorthwindTablesAndColumns.xlsx
+++ b/week-09/NorthwindTablesAndColumns.xlsx
@@ -4213,6 +4213,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ced60a7f-99b1-48d2-b555-34851c8026ae" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9e0b35a9-e6cb-436b-81d4-4440ba439ca5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="ced60a7f-99b1-48d2-b555-34851c8026ae">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <MediaLengthInSeconds xmlns="9e0b35a9-e6cb-436b-81d4-4440ba439ca5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CA5D0A6329BB324E86983B32928CFC2E" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3d7eac4bce3bbb09c82bd908806be82e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9e0b35a9-e6cb-436b-81d4-4440ba439ca5" xmlns:ns3="ced60a7f-99b1-48d2-b555-34851c8026ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eb51570e5b7cb8bd524bc2df5324d4a3" ns2:_="" ns3:_="">
     <xsd:import namespace="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
@@ -4453,25 +4472,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ced60a7f-99b1-48d2-b555-34851c8026ae" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9e0b35a9-e6cb-436b-81d4-4440ba439ca5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="ced60a7f-99b1-48d2-b555-34851c8026ae">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <MediaLengthInSeconds xmlns="9e0b35a9-e6cb-436b-81d4-4440ba439ca5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -4482,6 +4482,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BB560F9-4CC1-4243-8F16-7FDC2CD703FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ced60a7f-99b1-48d2-b555-34851c8026ae"/>
+    <ds:schemaRef ds:uri="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA285021-94D7-4152-B2E7-B2D9504C2DBD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4500,17 +4511,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BB560F9-4CC1-4243-8F16-7FDC2CD703FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ced60a7f-99b1-48d2-b555-34851c8026ae"/>
-    <ds:schemaRef ds:uri="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0257D61C-6042-483B-9C34-3DE0D82CB154}">
   <ds:schemaRefs>
